--- a/file/De-mi ตัวอย่างลงรายชื่อ (รพ.เมตตาธรรม).xlsx
+++ b/file/De-mi ตัวอย่างลงรายชื่อ (รพ.เมตตาธรรม).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Desktop/Tone/Dao/doc/AppBolt/demi-plus-web-v2/file/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6914A9-04A6-5B4B-B380-D54D48D8EAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0B2FDD-7CFC-FD49-B280-AB5F19B06792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{493625A2-FE23-49F0-8D72-420B791986D6}"/>
   </bookViews>
@@ -34,7 +34,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
+  <si>
+    <t>เลขบัตรประชาชน</t>
+  </si>
+  <si>
+    <t>วันเกิด</t>
+  </si>
+  <si>
+    <t>ชื่อ</t>
+  </si>
+  <si>
+    <t>นามสกุล</t>
+  </si>
+  <si>
+    <t>HN</t>
+  </si>
+  <si>
+    <t>เพศ</t>
+  </si>
+  <si>
+    <t>น้ำหนัก</t>
+  </si>
+  <si>
+    <t>ส่วนสูง</t>
+  </si>
+  <si>
+    <t>รอบเอว(ซม.)</t>
+  </si>
+  <si>
+    <t>ประเภทเบาหวาน</t>
+  </si>
+  <si>
+    <t>ค่าน้ำตาลในเลือด</t>
+  </si>
+  <si>
+    <t>ค่า HbA1c ล่าสุด (ถ้ามี)</t>
+  </si>
+  <si>
+    <t>โรงพยาบาล</t>
+  </si>
+  <si>
+    <t>บ้านเลขที่</t>
+  </si>
+  <si>
+    <t>หมู่ที่/ชุมชน</t>
+  </si>
+  <si>
+    <t>หมู่บ้าน</t>
+  </si>
+  <si>
+    <t>ซอย</t>
+  </si>
+  <si>
+    <t>ถนน</t>
+  </si>
+  <si>
+    <t>จังหวัด</t>
+  </si>
+  <si>
+    <t>อำเภอ</t>
+  </si>
+  <si>
+    <t>ตำบล</t>
+  </si>
+  <si>
+    <t>รหัสไปรษณีย์</t>
+  </si>
+  <si>
+    <t>ชื่อผู้ติดต่อ(ญาติ)</t>
+  </si>
+  <si>
+    <t>เบอร์โทร</t>
+  </si>
+  <si>
+    <t>ความสัมพันธ์</t>
+  </si>
+  <si>
+    <t>ชื่อผู้ดูแล (อสม.)</t>
+  </si>
   <si>
     <t>นายบุญเพ็ง</t>
   </si>
@@ -82,6 +160,9 @@
   </si>
   <si>
     <t>ไม่มี</t>
+  </si>
+  <si>
+    <t>รพ.สต.</t>
   </si>
   <si>
     <t>รพ.สต.บ้านฟ้าใส</t>
@@ -527,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304D6687-A08E-4522-B130-AE76F7E06B63}">
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="2" customWidth="1"/>
@@ -554,433 +635,519 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" s="2">
-        <v>5555555555555</v>
-      </c>
-      <c r="B1" s="3">
-        <v>236683</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>45688899</v>
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="H1">
-        <v>80</v>
-      </c>
-      <c r="I1">
-        <v>164</v>
-      </c>
-      <c r="J1">
-        <v>100</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="L1">
-        <v>140</v>
-      </c>
-      <c r="M1">
-        <v>6.8</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1">
-        <v>54</v>
-      </c>
-      <c r="Q1">
-        <v>12</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="W1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Y1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V1" t="s">
-        <v>32</v>
-      </c>
-      <c r="W1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X1">
-        <v>99000</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z1">
-        <v>857741248</v>
-      </c>
       <c r="AA1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="AB1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1234567890000</v>
+        <v>5555555555555</v>
       </c>
       <c r="B2" s="3">
-        <v>235359</v>
+        <v>236683</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>95562310</v>
+        <v>45688899</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>956321476</v>
+        <v>36</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="H2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I2">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="J2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="L2">
-        <v>105</v>
-      </c>
-      <c r="M2" t="s">
-        <v>14</v>
+        <v>140</v>
+      </c>
+      <c r="M2">
+        <v>6.8</v>
       </c>
       <c r="N2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="P2">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="Q2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R2" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="U2" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="V2" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="W2" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="X2">
         <v>99000</v>
       </c>
       <c r="Y2" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="Z2">
-        <v>946524875</v>
+        <v>857741248</v>
       </c>
       <c r="AA2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="AB2" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>9873216541234</v>
+        <v>1234567890000</v>
       </c>
       <c r="B3" s="3">
-        <v>230464</v>
+        <v>235359</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>74125836</v>
+        <v>95562310</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>625458792</v>
+        <v>956321476</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I3">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="J3">
         <v>95</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>130</v>
-      </c>
-      <c r="M3">
-        <v>6.9</v>
+        <v>105</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
       </c>
       <c r="N3" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="O3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="P3">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="Q3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R3" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="S3" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="T3" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="U3" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="V3" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="W3" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="X3">
         <v>99000</v>
       </c>
       <c r="Y3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="Z3">
-        <v>681245568</v>
+        <v>946524875</v>
       </c>
       <c r="AA3" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="AB3" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>1478523691472</v>
+        <v>9873216541234</v>
       </c>
       <c r="B4" s="3">
-        <v>223020</v>
+        <v>230464</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>59123458</v>
+        <v>74125836</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>921247854</v>
+        <v>625458792</v>
       </c>
       <c r="H4">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="I4">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="J4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="L4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="N4" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="O4" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="Q4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R4" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="S4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="T4" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="U4" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="V4" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="W4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="X4">
         <v>99000</v>
       </c>
       <c r="Y4" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="Z4">
-        <v>968745523</v>
+        <v>681245568</v>
       </c>
       <c r="AA4" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="AB4" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>3698741236987</v>
+        <v>1478523691472</v>
       </c>
       <c r="B5" s="3">
-        <v>219792</v>
+        <v>223020</v>
       </c>
       <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5">
+        <v>59123458</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5">
+        <v>921247854</v>
+      </c>
+      <c r="H5">
+        <v>99</v>
+      </c>
+      <c r="I5">
+        <v>161</v>
+      </c>
+      <c r="J5">
+        <v>110</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5">
+        <v>120</v>
+      </c>
+      <c r="M5">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>14753069</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>812443615</v>
-      </c>
-      <c r="H5">
-        <v>102</v>
-      </c>
-      <c r="I5">
-        <v>159</v>
-      </c>
-      <c r="J5">
-        <v>103</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5">
-        <v>119</v>
-      </c>
-      <c r="M5">
-        <v>7.32</v>
-      </c>
       <c r="N5" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="O5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="S5" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="T5" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="U5" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="V5" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="W5" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="X5">
         <v>99000</v>
       </c>
       <c r="Y5" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="Z5">
+        <v>968745523</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>3698741236987</v>
+      </c>
+      <c r="B6" s="3">
+        <v>219792</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6">
+        <v>14753069</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6">
+        <v>812443615</v>
+      </c>
+      <c r="H6">
+        <v>102</v>
+      </c>
+      <c r="I6">
+        <v>159</v>
+      </c>
+      <c r="J6">
+        <v>103</v>
+      </c>
+      <c r="K6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6">
+        <v>119</v>
+      </c>
+      <c r="M6">
+        <v>7.32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6">
+        <v>98</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" t="s">
+        <v>52</v>
+      </c>
+      <c r="U6" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" t="s">
+        <v>59</v>
+      </c>
+      <c r="W6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X6">
+        <v>99000</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z6">
         <v>845631247</v>
       </c>
-      <c r="AA5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>44</v>
+      <c r="AA6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/file/De-mi ตัวอย่างลงรายชื่อ (รพ.เมตตาธรรม).xlsx
+++ b/file/De-mi ตัวอย่างลงรายชื่อ (รพ.เมตตาธรรม).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Desktop/Tone/Dao/doc/AppBolt/demi-plus-web-v2/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0B2FDD-7CFC-FD49-B280-AB5F19B06792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736807F8-E2A8-2740-8279-CCCADDDF5921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{493625A2-FE23-49F0-8D72-420B791986D6}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="10560" xr2:uid="{493625A2-FE23-49F0-8D72-420B791986D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,9 +102,6 @@
     <t>รหัสไปรษณีย์</t>
   </si>
   <si>
-    <t>ชื่อผู้ติดต่อ(ญาติ)</t>
-  </si>
-  <si>
     <t>เบอร์โทร</t>
   </si>
   <si>
@@ -250,6 +247,9 @@
   </si>
   <si>
     <t>นายศักดา ประกาศ</t>
+  </si>
+  <si>
+    <t>ชื่อผู้ติดต่อ</t>
   </si>
 </sst>
 </file>
@@ -654,7 +654,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -678,7 +678,7 @@
         <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P1" t="s">
         <v>13</v>
@@ -708,16 +708,16 @@
         <v>21</v>
       </c>
       <c r="Y1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>24</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
@@ -728,19 +728,19 @@
         <v>236683</v>
       </c>
       <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
         <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
       </c>
       <c r="E2">
         <v>45688899</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2">
         <v>80</v>
@@ -752,7 +752,7 @@
         <v>100</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L2">
         <v>140</v>
@@ -761,10 +761,10 @@
         <v>6.8</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P2">
         <v>54</v>
@@ -773,37 +773,37 @@
         <v>12</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" t="s">
         <v>56</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
         <v>57</v>
-      </c>
-      <c r="V2" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" t="s">
-        <v>58</v>
       </c>
       <c r="X2">
         <v>99000</v>
       </c>
       <c r="Y2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z2">
         <v>857741248</v>
       </c>
       <c r="AA2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -814,16 +814,16 @@
         <v>235359</v>
       </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
       </c>
       <c r="E3">
         <v>95562310</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3">
         <v>956321476</v>
@@ -838,19 +838,19 @@
         <v>95</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L3">
         <v>105</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P3">
         <v>85</v>
@@ -859,37 +859,37 @@
         <v>5</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X3">
         <v>99000</v>
       </c>
       <c r="Y3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z3">
         <v>946524875</v>
       </c>
       <c r="AA3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -900,16 +900,16 @@
         <v>230464</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
       </c>
       <c r="E4">
         <v>74125836</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4">
         <v>625458792</v>
@@ -924,7 +924,7 @@
         <v>95</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L4">
         <v>130</v>
@@ -933,10 +933,10 @@
         <v>6.9</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P4">
         <v>12</v>
@@ -945,37 +945,37 @@
         <v>4</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X4">
         <v>99000</v>
       </c>
       <c r="Y4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z4">
         <v>681245568</v>
       </c>
       <c r="AA4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -986,16 +986,16 @@
         <v>223020</v>
       </c>
       <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
         <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
       </c>
       <c r="E5">
         <v>59123458</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5">
         <v>921247854</v>
@@ -1010,7 +1010,7 @@
         <v>110</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L5">
         <v>120</v>
@@ -1019,10 +1019,10 @@
         <v>8</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P5">
         <v>136</v>
@@ -1031,37 +1031,37 @@
         <v>8</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V5" t="s">
+        <v>58</v>
+      </c>
+      <c r="W5" t="s">
         <v>59</v>
-      </c>
-      <c r="W5" t="s">
-        <v>60</v>
       </c>
       <c r="X5">
         <v>99000</v>
       </c>
       <c r="Y5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z5">
         <v>968745523</v>
       </c>
       <c r="AA5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -1072,16 +1072,16 @@
         <v>219792</v>
       </c>
       <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
         <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
       </c>
       <c r="E6">
         <v>14753069</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6">
         <v>812443615</v>
@@ -1096,7 +1096,7 @@
         <v>103</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6">
         <v>119</v>
@@ -1105,10 +1105,10 @@
         <v>7.32</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P6">
         <v>98</v>
@@ -1117,37 +1117,37 @@
         <v>2</v>
       </c>
       <c r="R6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X6">
         <v>99000</v>
       </c>
       <c r="Y6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Z6">
         <v>845631247</v>
       </c>
       <c r="AA6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
